--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G629"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17413,6 +17413,168 @@
         <v>397.87</v>
       </c>
       <c r="G629" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>396.48</v>
+      </c>
+      <c r="C630" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="D630" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="E630" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="F630" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>396.11</v>
+      </c>
+      <c r="C631" t="n">
+        <v>386.58</v>
+      </c>
+      <c r="D631" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="E631" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="F631" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>397.11</v>
+      </c>
+      <c r="C632" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="D632" t="n">
+        <v>383.54</v>
+      </c>
+      <c r="E632" t="n">
+        <v>370.03</v>
+      </c>
+      <c r="F632" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>396.51</v>
+      </c>
+      <c r="C633" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D633" t="n">
+        <v>382.87</v>
+      </c>
+      <c r="E633" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="F633" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="C634" t="n">
+        <v>384.99</v>
+      </c>
+      <c r="D634" t="n">
+        <v>382.87</v>
+      </c>
+      <c r="E634" t="n">
+        <v>370.36</v>
+      </c>
+      <c r="F634" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>396.86</v>
+      </c>
+      <c r="C635" t="n">
+        <v>384.75</v>
+      </c>
+      <c r="D635" t="n">
+        <v>382.65</v>
+      </c>
+      <c r="E635" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="F635" t="n">
+        <v>397.32</v>
+      </c>
+      <c r="G635" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17429,7 +17591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B756"/>
+  <dimension ref="A1:B762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24992,6 +25154,66 @@
       </c>
       <c r="B756" t="n">
         <v>-0.79</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -25160,28 +25382,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03503912031678685</v>
+        <v>0.02897705603379698</v>
       </c>
       <c r="J2" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K2" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002823676984274659</v>
+        <v>0.001963816756659686</v>
       </c>
       <c r="M2" t="n">
-        <v>4.020599564394788</v>
+        <v>4.009596352022161</v>
       </c>
       <c r="N2" t="n">
-        <v>25.83037498793877</v>
+        <v>25.69544005840216</v>
       </c>
       <c r="O2" t="n">
-        <v>5.082359195092253</v>
+        <v>5.069066981053038</v>
       </c>
       <c r="P2" t="n">
-        <v>399.122478745268</v>
+        <v>399.1855186345891</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -25242,28 +25464,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06162127933723342</v>
+        <v>0.05011396432229918</v>
       </c>
       <c r="J3" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K3" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006564952840370397</v>
+        <v>0.004388752778346605</v>
       </c>
       <c r="M3" t="n">
-        <v>4.479221623416709</v>
+        <v>4.490791826398091</v>
       </c>
       <c r="N3" t="n">
-        <v>34.23234622982584</v>
+        <v>34.30586774040952</v>
       </c>
       <c r="O3" t="n">
-        <v>5.850841497581851</v>
+        <v>5.857121113687979</v>
       </c>
       <c r="P3" t="n">
-        <v>390.5317583515189</v>
+        <v>390.6514457278336</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25320,28 +25542,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1120403996315785</v>
+        <v>0.1046470855794017</v>
       </c>
       <c r="J4" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K4" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02802513692989184</v>
+        <v>0.02486842031167258</v>
       </c>
       <c r="M4" t="n">
-        <v>3.992953898221047</v>
+        <v>3.992505408046462</v>
       </c>
       <c r="N4" t="n">
-        <v>25.93725231801979</v>
+        <v>25.85660560872756</v>
       </c>
       <c r="O4" t="n">
-        <v>5.092862880347338</v>
+        <v>5.084939095872</v>
       </c>
       <c r="P4" t="n">
-        <v>384.5224520730877</v>
+        <v>384.599351024411</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25398,28 +25620,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005373919326451398</v>
+        <v>-0.01002043991004312</v>
       </c>
       <c r="J5" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K5" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>4.873109816827537e-05</v>
+        <v>0.0001694668850416026</v>
       </c>
       <c r="M5" t="n">
-        <v>4.83054531634692</v>
+        <v>4.866269757305509</v>
       </c>
       <c r="N5" t="n">
-        <v>35.30386880899144</v>
+        <v>35.67116865007219</v>
       </c>
       <c r="O5" t="n">
-        <v>5.941705883750174</v>
+        <v>5.972534524812074</v>
       </c>
       <c r="P5" t="n">
-        <v>378.9807439888721</v>
+        <v>379.1408402349248</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25476,28 +25698,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0719971055776945</v>
+        <v>0.07589019085940235</v>
       </c>
       <c r="J6" t="n">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="K6" t="n">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01067915407270903</v>
+        <v>0.01207031700073802</v>
       </c>
       <c r="M6" t="n">
-        <v>4.254001090390291</v>
+        <v>4.22924373017543</v>
       </c>
       <c r="N6" t="n">
-        <v>28.18535730600025</v>
+        <v>27.96680267451712</v>
       </c>
       <c r="O6" t="n">
-        <v>5.308988350524067</v>
+        <v>5.288364839391957</v>
       </c>
       <c r="P6" t="n">
-        <v>393.1409158361729</v>
+        <v>393.0999637469931</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25535,7 +25757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G629"/>
+  <dimension ref="A1:G635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48799,6 +49021,228 @@
         </is>
       </c>
     </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-36.36879413685881,174.83735576201533</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-36.369125898467566,174.8381070248735</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-36.36927814942936,174.83894524877428</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-36.369464350074935,174.8398133334037</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-36.36927884486664,174.840721596097</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-36.36879725410547,174.8373542978348</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-36.36912928821074,174.83810587577534</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-36.36928109953329,174.83894478276008</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-36.36946641857684,174.83981316761205</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-36.36927884486664,174.840721596097</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-36.36878882911447,174.83735825507932</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-36.36913754527739,174.8381030766897</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-36.36928467541686,174.83894421789438</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-36.369471634799005,174.83981274952873</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-36.369258052091,174.84072287655297</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-36.36879388410908,174.8373558807327</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-36.369142151851385,174.83810151509428</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-36.369290665021815,174.8389432717442</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-36.36947388317062,174.8398125693204</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-36.369270833797245,174.84072208943292</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-36.36879211486097,174.83735671175404</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-36.36914310793277,174.83810119098953</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-36.369290665021815,174.8389432717442</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-36.36946866694846,174.83981298740372</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-36.369270833797245,174.84072208943292</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-36.36879093536222,174.83735726576828</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-36.36914519392854,174.83810048385195</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-36.36929263175775,174.838942961068</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-36.369465069553854,174.83981327573704</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-36.369270833797245,174.84072208943292</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0127/nzd0127.xlsx
+++ b/data/nzd0127/nzd0127.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17575,6 +17575,87 @@
         <v>397.32</v>
       </c>
       <c r="G635" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>397.58</v>
+      </c>
+      <c r="C636" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="D636" t="n">
+        <v>383.08</v>
+      </c>
+      <c r="E636" t="n">
+        <v>371.59</v>
+      </c>
+      <c r="F636" t="n">
+        <v>397.91</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>398.25</v>
+      </c>
+      <c r="C637" t="n">
+        <v>385.55</v>
+      </c>
+      <c r="D637" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="E637" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="F637" t="n">
+        <v>398.35</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>398.28</v>
+      </c>
+      <c r="C638" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="D638" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="E638" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="F638" t="n">
+        <v>398.68</v>
+      </c>
+      <c r="G638" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17591,7 +17672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B762"/>
+  <dimension ref="A1:B765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25214,6 +25295,36 @@
       </c>
       <c r="B762" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -25382,28 +25493,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02897705603379698</v>
+        <v>0.02728573350129307</v>
       </c>
       <c r="J2" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001963816756659686</v>
+        <v>0.001757777075795053</v>
       </c>
       <c r="M2" t="n">
-        <v>4.009596352022161</v>
+        <v>3.998309018421019</v>
       </c>
       <c r="N2" t="n">
-        <v>25.69544005840216</v>
+        <v>25.59227487338844</v>
       </c>
       <c r="O2" t="n">
-        <v>5.069066981053038</v>
+        <v>5.05888079256553</v>
       </c>
       <c r="P2" t="n">
-        <v>399.1855186345891</v>
+        <v>399.2031670975473</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -25464,28 +25575,28 @@
         <v>0.0419</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05011396432229918</v>
+        <v>0.04421712105431873</v>
       </c>
       <c r="J3" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004388752778346605</v>
+        <v>0.003432867652505944</v>
       </c>
       <c r="M3" t="n">
-        <v>4.490791826398091</v>
+        <v>4.497408666509929</v>
       </c>
       <c r="N3" t="n">
-        <v>34.30586774040952</v>
+        <v>34.35547130365714</v>
       </c>
       <c r="O3" t="n">
-        <v>5.857121113687979</v>
+        <v>5.861354050358768</v>
       </c>
       <c r="P3" t="n">
-        <v>390.6514457278336</v>
+        <v>390.7129827776359</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25542,28 +25653,28 @@
         <v>0.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1046470855794017</v>
+        <v>0.1009634183730315</v>
       </c>
       <c r="J4" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02486842031167258</v>
+        <v>0.02334139981427497</v>
       </c>
       <c r="M4" t="n">
-        <v>3.992505408046462</v>
+        <v>3.992346889821681</v>
       </c>
       <c r="N4" t="n">
-        <v>25.85660560872756</v>
+        <v>25.81721907031502</v>
       </c>
       <c r="O4" t="n">
-        <v>5.084939095872</v>
+        <v>5.08106475754</v>
       </c>
       <c r="P4" t="n">
-        <v>384.599351024411</v>
+        <v>384.6377927921348</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25620,28 +25731,28 @@
         <v>0.0534</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01002043991004312</v>
+        <v>-0.01604485276770079</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0001694668850416026</v>
+        <v>0.0004360053684323573</v>
       </c>
       <c r="M5" t="n">
-        <v>4.866269757305509</v>
+        <v>4.874872303403248</v>
       </c>
       <c r="N5" t="n">
-        <v>35.67116865007219</v>
+        <v>35.72364180788747</v>
       </c>
       <c r="O5" t="n">
-        <v>5.972534524812074</v>
+        <v>5.976925782363997</v>
       </c>
       <c r="P5" t="n">
-        <v>379.1408402349248</v>
+        <v>379.2037078350264</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25698,28 +25809,28 @@
         <v>0.0571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07589019085940235</v>
+        <v>0.07869174519546682</v>
       </c>
       <c r="J6" t="n">
+        <v>637</v>
+      </c>
+      <c r="K6" t="n">
         <v>634</v>
       </c>
-      <c r="K6" t="n">
-        <v>631</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01207031700073802</v>
+        <v>0.01307289234261388</v>
       </c>
       <c r="M6" t="n">
-        <v>4.22924373017543</v>
+        <v>4.22048247732633</v>
       </c>
       <c r="N6" t="n">
-        <v>27.96680267451712</v>
+        <v>27.88153354347868</v>
       </c>
       <c r="O6" t="n">
-        <v>5.288364839391957</v>
+        <v>5.280296728733972</v>
       </c>
       <c r="P6" t="n">
-        <v>393.0999637469931</v>
+        <v>393.0703946565145</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25757,7 +25868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G635"/>
+  <dimension ref="A1:G638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49243,6 +49354,117 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.36878486936865,174.83736011498397</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.369143542515225,174.8381010436692</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.36928878768294,174.83894356829876</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.369457604960054,174.8398138740286</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.369265523088316,174.84072241647576</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.36877922462458,174.8373627663371</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.36913824060931,174.83810284097717</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.36928574818193,174.83894404843468</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.36945202899841,174.83981432094512</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.36926156255963,174.84072266037214</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.368778971874846,174.83736288505438</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.36914032660509,174.83810213383964</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.36928807250622,174.83894368127193</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.3694525686076,174.83981427769515</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.3692585921631,174.84072284329437</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
